--- a/068270 Celltrion.xlsx
+++ b/068270 Celltrion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0CE7EE-59C4-45DC-941D-18DC9A6DE2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D29103-2FA2-479D-ABA1-80ACEDEB4D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27015" yWindow="750" windowWidth="26490" windowHeight="19650" xr2:uid="{223FD510-5E13-4D33-AFCD-863DA9D9CCA4}"/>
+    <workbookView xWindow="350" yWindow="1040" windowWidth="19050" windowHeight="19840" xr2:uid="{223FD510-5E13-4D33-AFCD-863DA9D9CCA4}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,6 +37,24 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={CC8C1A5C-FB80-42EE-B9A8-C8915CDA669A}</author>
+  </authors>
+  <commentList>
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{CC8C1A5C-FB80-42EE-B9A8-C8915CDA669A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Celltrion Inc</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="52">
   <si>
@@ -181,9 +199,6 @@
     <t>PD1 (Keytruda?)</t>
   </si>
   <si>
-    <t>Q224</t>
-  </si>
-  <si>
     <t>COGS</t>
   </si>
   <si>
@@ -194,13 +209,16 @@
   </si>
   <si>
     <t>Gross Profit</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -212,6 +230,12 @@
       <sz val="10"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -358,6 +382,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Martin Shkreli" id="{E5F3659C-855A-44B6-B230-CFAB3C8E64FA}" userId="9ffda80931a57275" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -655,18 +685,26 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="J3" dT="2026-08-01T14:56:03.38" personId="{E5F3659C-855A-44B6-B230-CFAB3C8E64FA}" id="{CC8C1A5C-FB80-42EE-B9A8-C8915CDA669A}">
+    <text>Celltrion Inc</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1640841-9D06-48FC-A361-9BE42E08264D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1640841-9D06-48FC-A361-9BE42E08264D}">
   <dimension ref="B2:K19"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" customWidth="1"/>
+    <col min="1" max="1" width="3.453125" customWidth="1"/>
     <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" customWidth="1"/>
-    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.453125" customWidth="1"/>
+    <col min="10" max="10" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
@@ -679,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>169100</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+        <v>186700</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
@@ -691,13 +729,13 @@
         <v>1</v>
       </c>
       <c r="J3" s="1">
-        <v>142.48709700000001</v>
+        <v>230.96096900000001</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="7" t="s">
         <v>8</v>
       </c>
@@ -707,11 +745,11 @@
       </c>
       <c r="J4" s="1">
         <f>+J2*J3</f>
-        <v>24094568.102700002</v>
+        <v>43120412.912299998</v>
       </c>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
@@ -720,14 +758,13 @@
         <v>3</v>
       </c>
       <c r="J5" s="1">
-        <f>564612+193825+30385</f>
-        <v>788822</v>
+        <v>1199000</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="7" t="s">
         <v>35</v>
       </c>
@@ -736,14 +773,13 @@
         <v>4</v>
       </c>
       <c r="J6" s="1">
-        <f>1783369+107116</f>
-        <v>1890485</v>
+        <v>3826000</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
         <v>36</v>
       </c>
@@ -753,10 +789,10 @@
       </c>
       <c r="J7" s="1">
         <f>+J4-J5+J6</f>
-        <v>25196231.102700002</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+        <v>45747412.912299998</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -764,67 +800,67 @@
       <c r="F8" s="5"/>
       <c r="G8" s="6"/>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>37</v>
       </c>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
         <v>38</v>
       </c>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
         <v>39</v>
       </c>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
         <v>40</v>
       </c>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
         <v>41</v>
       </c>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
         <v>42</v>
       </c>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
         <v>43</v>
       </c>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
         <v>44</v>
       </c>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
         <v>45</v>
       </c>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
         <v>46</v>
       </c>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="9"/>
       <c r="C19" s="10"/>
       <c r="D19" s="10"/>
@@ -835,24 +871,25 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{494D976F-FCD5-4971-ABB0-7BAF4093FAD3}">
   <dimension ref="A1:AC11"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="18" width="9.140625" style="2"/>
+    <col min="3" max="18" width="9.1796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
@@ -905,31 +942,31 @@
         <v>2020</v>
       </c>
       <c r="X2">
-        <f>+W2+1</f>
+        <f t="shared" ref="X2:AC2" si="0">+W2+1</f>
         <v>2021</v>
       </c>
       <c r="Y2">
-        <f>+X2+1</f>
+        <f t="shared" si="0"/>
         <v>2022</v>
       </c>
       <c r="Z2">
-        <f>+Y2+1</f>
+        <f t="shared" si="0"/>
         <v>2023</v>
       </c>
       <c r="AA2">
-        <f>+Z2+1</f>
+        <f t="shared" si="0"/>
         <v>2024</v>
       </c>
       <c r="AB2">
-        <f>+AA2+1</f>
+        <f t="shared" si="0"/>
         <v>2025</v>
       </c>
       <c r="AC2">
-        <f>+AB2+1</f>
+        <f t="shared" si="0"/>
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
@@ -966,9 +1003,9 @@
         <v>2176.4319999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -993,9 +1030,9 @@
         <v>1124.5630000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -1022,9 +1059,9 @@
         <v>1051.8689999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
@@ -1049,9 +1086,9 @@
         <v>400.38799999999998</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -1078,24 +1115,24 @@
         <v>651.48099999999977</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="Z8" s="1">
         <f>54.185-34.743+31.438-19.95</f>
         <v>30.929999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="Z9" s="1">
         <f>+Z7+Z8</f>
         <v>682.41099999999972</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="Z10" s="1">
         <v>131.38900000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="Z11" s="1">
         <f>+Z9-Z10</f>
         <v>551.02199999999971</v>
@@ -1112,18 +1149,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FCA40F5-E645-49FC-AE33-102DC0BFF0C6}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>6</v>
       </c>
@@ -1131,7 +1168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>28</v>
       </c>
@@ -1139,7 +1176,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>30</v>
       </c>
@@ -1147,7 +1184,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>32</v>
       </c>
@@ -1155,7 +1192,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>34</v>
       </c>
